--- a/models/xls/BeModelChildReport.xlsx
+++ b/models/xls/BeModelChildReport.xlsx
@@ -504,7 +504,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -940,23 +939,11 @@
           <t>Data Element</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Common Glossary</t>
         </is>
       </c>
-      <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Example Value</t>
@@ -1054,8 +1041,6 @@
           <t>dateTime</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1076,7 +1061,16 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1212,6 +1206,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1352,6 +1356,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1527,6 +1541,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1667,6 +1691,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1852,6 +1886,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2002,6 +2046,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2177,6 +2231,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2397,6 +2461,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2572,6 +2646,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2755,6 +2839,16 @@
       <c r="K51" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>equivalent</t>
         </is>
       </c>
     </row>
